--- a/docs/res/企业节假日放假.xlsx
+++ b/docs/res/企业节假日放假.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\work_space\agent-driven_gen\docs\res\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D593D96-9625-4D09-BFE5-091CBDC5690E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD95F0BF-8B91-4C5E-810B-8A01606099AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="16">
   <si>
     <t>年份</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -75,6 +75,14 @@
   </si>
   <si>
     <t>补班时间</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>元旦</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026年1月1日到2026年1月3日</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -405,7 +413,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="35.36328125" customWidth="1"/>
@@ -431,13 +439,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>9</v>
+        <v>15</v>
+      </c>
+      <c r="D2" s="2">
+        <v>46026</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -445,10 +453,13 @@
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -456,13 +467,10 @@
         <v>1</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" s="2">
-        <v>46151</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -470,9 +478,23 @@
         <v>1</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="2">
+        <v>46151</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C6" s="1" t="s">
         <v>12</v>
       </c>
     </row>
